--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_804_Ukraine.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_804_Ukraine.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2e16a733d4e64a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8d20328bc33b443c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7aca4c21660f471b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5487d91e60c24dc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ree71a169c7a84e00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra2bab0cadcb04aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re29488446bbc4cf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R3872a39b88d74748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2e42746d3dde48ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf1ea980a421c4ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rbb2fbdf685904245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R15d733a537ff42e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ804CommercialTable" displayName="EEZ804CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ804CommercialTable" displayName="EEZ804CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ804FunctionalTable" displayName="EEZ804FunctionalTable" ref="A1:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O16"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ804FunctionalTable" displayName="EEZ804FunctionalTable" ref="A1:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E16"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ804ValidationTable" displayName="EEZ804ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ804ValidationTable" displayName="EEZ804ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -2570,7 +2524,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7c7ccbac94a41cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R962e0551236f4e51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,20 +2534,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2601,606 +2545,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1171.733787871</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1171.733787871</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$29,A2,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>150948.5526928513</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>150948.5526928513</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2652.4900788192</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2652.4900788192</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$29,A3,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>6076503.72085435</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>6076503.72085435</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2099.0933285592</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.97260037008466</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>93.8858991922781</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2099.0933285592</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>116.13010992389562</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$29,A4,'Species'!$U$2:$U$29))</x:f>
-        <x:v>243767.93898609583</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.97260037008466</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>93.8858991922781</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>197075.26464029256</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>46692.67434580327</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2369281321581787</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.23692813215817868</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>955.8347947850001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.357131745548861</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2275.7876984124987</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>955.8347947850001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2285.1257988742022</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$29,A5,'Species'!$U$2:$U$29))</x:f>
-        <x:v>2184202.7490248326</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.357131745548861</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2275.7876984124987</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2175277.0676863384</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>8925.681338494178</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.004103238833841</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.004103238833840916</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>8691.783426827002</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0053866354268264</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>101.24804249563333</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>8691.783426827002</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>103.61481383920972</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$29,A6,'Species'!$U$2:$U$29))</x:f>
-        <x:v>900597.5217014081</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0053866354268264</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>101.24804249563333</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>880026.0577622218</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>20571.463939186302</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0233759713791846</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.023375971379184547</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2718.8566269312996</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.69</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>48.97788193684461</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2718.8566269312996</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>48.97788193684462</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$29,A7,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>133163.83887704878</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.69</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>48.97788193684461</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>133163.83887704878</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>19313.298430049</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2614304264268945</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>182.5704249519449</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>19313.298430049</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>186.82230273478797</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$29,A8,'Species'!$U$2:$U$29))</x:f>
-        <x:v>3608154.8861059193</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2614304264268945</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>182.5704249519449</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3526037.1015977757</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>82117.78450814355</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0232889734685244</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.02328897346852448</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>26378.5293235529</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.1902816291708853</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>154.98213136963395</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>26378.5293235529</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>291.203006976862</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$29,A9,'Species'!$U$2:$U$29))</x:f>
-        <x:v>7681507.058645934</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.1902816291708853</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>154.98213136963395</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4088200.696960617</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3593306.361685317</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.8789456849211854</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.8789456849211854</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1630.4753181773</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.066913281120613</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1166.5766545776546</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1630.4753181773</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1571.66034530219</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$29,A10,'Species'!$U$2:$U$29))</x:f>
-        <x:v>2562553.401573234</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.066913281120613</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1166.5766545776546</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1902074.4420507117</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>660478.959522522</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.347241382840111</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.3472413828401112</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>291.62890808500003</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>291.62890808500003</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$29,A11,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>922211.5810964933</x:v>
       </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>922211.5810964933</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1be18427ee9c4f52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f50c8f9804a4b7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3210,20 +2760,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3231,876 +2771,307 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>953.1986626651001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>953.1986626651001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$29,A2,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2183651.98296098</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>2183651.98296098</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>992.5558898298</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.53</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>3388.4415613920273</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>992.5558898298</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$29,A3,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3363217.6291037407</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.53</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>3363217.6291037407</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>650.4868274331</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6102991212746627</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>407.6609585104424</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>650.4868274331</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>407.75021369064814</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$29,A4,'Species'!$U$2:$U$29))</x:f>
-        <x:v>265236.14288879826</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6102991212746627</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>407.6609585104424</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>265178.08356979425</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>58.05931900400901</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0002189446360816</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0002189446360816162</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>979.9884907442</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.37</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2344.228815319923</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>979.9884907442</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2344.228815319923</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$29,A5,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2297317.2586844354</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.37</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2344.228815319923</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>2297317.2586844354</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>35.97811447710001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.43</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>269.1534803926917</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>35.97811447710001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>269.1534803926917</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$29,A6,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>9683.634729478154</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.43</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>269.1534803926917</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>9683.634729478154</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2652.4900788192</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2652.4900788192</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$29,A7,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6076503.72085435</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>6076503.72085435</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>19741.112829924</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.219523002680517</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>165.7765139097362</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>19741.112829924</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>180.32729352791276</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$29,A8,'Species'!$U$2:$U$29))</x:f>
-        <x:v>3559861.4478493496</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.219523002680517</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>165.7765139097362</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3272612.865643568</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>287248.5822057817</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0877734684787697</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.08777346847876964</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2750.9362941549</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8500748936678764</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>708.0678794845898</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2750.9362941549</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>866.7014738532152</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$29,A9,'Species'!$U$2:$U$29))</x:f>
-        <x:v>2384240.540620354</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8500748936678764</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>708.0678794845898</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1947849.628399456</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>436390.9122208981</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2240372695398871</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.22403726953988723</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>527.8670123261</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.304041896131188</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>201.39185220174008</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>527.8670123261</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>245.72115110545133</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$29,A10,'Species'!$U$2:$U$29))</x:f>
-        <x:v>129708.08989936477</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.304041896131188</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>201.39185220174008</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>106308.11532855206</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>23399.974570812716</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2201146591536647</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.2201146591536647</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3114.0633569833</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.657003320731065</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>45.39450876217534</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3114.0633569833</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>46.177919033466544</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$29,A11,'Species'!$U$2:$U$29))</x:f>
-        <x:v>143800.96556385985</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.657003320731065</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>45.39450876217534</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>141361.37634454758</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2439.589219312271</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.017257820222167</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.017257820222166844</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2063.1152140821</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.9646239002614765</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>92.17728246207763</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2063.1152140821</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>113.46157628950648</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$29,A12,'Species'!$U$2:$U$29))</x:f>
-        <x:v>234084.30425661767</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.9646239002614765</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>92.17728246207763</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>190172.3538402555</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>43911.950416362175</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.230906067730792</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.23090606773079198</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>202.75</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.22</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>165.95869074375614</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>202.75</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>165.9586907437561</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$29,A13,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>33648.12454829655</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.22</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>165.95869074375614</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>33648.12454829655</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>9974.300814136102</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.0172612046605427</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>104.05458097356488</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>9974.300814136102</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>104.56863006797975</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$29,A14,'Species'!$U$2:$U$29))</x:f>
-        <x:v>1042998.9720201474</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.0172612046605427</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>104.05458097356488</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1037871.6917192192</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5127.280300928163</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0049401870595727</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.004940187059572748</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>21262.244305961998</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>21262.244305961998</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$29,A15,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2739107.669514543</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>2739107.669514543</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2.6361321199</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.32</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>208.92961308540387</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2.6361321199</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>208.92961308540387</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$29,A16,'Species'!$U$2:$U$29))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>550.7660638527125</x:v>
       </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.32</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>208.92961308540387</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>550.7660638527125</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O16">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R168dbdeba3d74380"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a3b24be6325432a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4275,7 +3246,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -4374,7 +3345,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>24463611.249558166</x:v>
+        <x:v>20051518.324218698</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4388,7 +3359,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>24463611.249558173</x:v>
+        <x:v>23665034.901305072</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4402,7 +3373,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4412092.925339468</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4416,7 +3387,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>7.450580596923828e-9</x:v>
+        <x:v>-798576.3482530937</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4427,9 +3398,9 @@
         <x:v>EEZ_804</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -4441,47 +3412,19 @@
         <x:v>EEZ_804</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_804</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_804</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc3a785c94b4423c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8992bc9d80d146b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4528,7 +3471,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
